--- a/QCM4_1_MATH.xlsx
+++ b/QCM4_1_MATH.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA58CBAD-F7E9-4FF2-B6D9-A7E81550F2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F226586-096E-420E-AC94-F34530824BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="QCM_Suites" sheetId="1" r:id="rId1"/>
+    <sheet name="QCM_Nombres complexes" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="106">
   <si>
     <t>Question</t>
   </si>
@@ -150,9 +150,6 @@
     <t>$\sqrt{5}e^{i\frac{\pi}{2}}$</t>
   </si>
   <si>
-    <t>$-\sqrt{5}(1-i)$ (Option D)</t>
-  </si>
-  <si>
     <t>$\frac{\sqrt{2}}{2}$</t>
   </si>
   <si>
@@ -162,9 +159,6 @@
     <t>$\frac{\sqrt{2}}{2}e^{i\pi}$</t>
   </si>
   <si>
-    <t>$\frac{\sqrt{2}}{2}e^{i\pi}$ (Option E)</t>
-  </si>
-  <si>
     <t>$\frac{\sqrt{6}+\sqrt{2}}{4}+i\frac{\sqrt{6}-\sqrt{2}}{4}$</t>
   </si>
   <si>
@@ -180,9 +174,6 @@
     <t>$5e^{i\frac{\pi}{12}}$</t>
   </si>
   <si>
-    <t>$5e^{-i\frac{\pi}{12}}$ (Option D)</t>
-  </si>
-  <si>
     <t>$\frac{\sqrt{6}+\sqrt{2}}{4}$</t>
   </si>
   <si>
@@ -210,9 +201,6 @@
     <t>Un complexe dont $\mathcal{Re}(Z_8)\times \mathcal{Im}(Z_8) \ne 0$</t>
   </si>
   <si>
-    <t>Un réel négatif (Option B)</t>
-  </si>
-  <si>
     <t>Equilatéral</t>
   </si>
   <si>
@@ -228,9 +216,6 @@
     <t>Non isocèle et non rectangle en $A_5$</t>
   </si>
   <si>
-    <t>Rectangle et isocèle en $A_5$ (Option B)</t>
-  </si>
-  <si>
     <t>Rectangle</t>
   </si>
   <si>
@@ -246,9 +231,6 @@
     <t>Trapèze</t>
   </si>
   <si>
-    <t>Carré (Option B)</t>
-  </si>
-  <si>
     <t>$\cos(\theta)$</t>
   </si>
   <si>
@@ -264,9 +246,6 @@
     <t>$\sin(\theta/2)$</t>
   </si>
   <si>
-    <t>$2\cos(\theta/2)$ (Option C)</t>
-  </si>
-  <si>
     <t>$\theta/2+\pi$</t>
   </si>
   <si>
@@ -279,9 +258,6 @@
     <t>$\theta+\pi$</t>
   </si>
   <si>
-    <t>$\theta/2$ (Option D)</t>
-  </si>
-  <si>
     <t>$5\pi/12 [2\pi]$</t>
   </si>
   <si>
@@ -297,21 +273,12 @@
     <t>$\pi/2 [2\pi]$</t>
   </si>
   <si>
-    <t>$5\pi/12 [2\pi]$ (Option A)</t>
-  </si>
-  <si>
     <t>Un complexe dont $\mathcal{Re}(b^6)\times \mathcal{Im}(b^6) \ne 0$</t>
   </si>
   <si>
-    <t>Un imaginaire pur dont la partie imaginaire est positive (Option C)</t>
-  </si>
-  <si>
     <t>$5$</t>
   </si>
   <si>
-    <t>$3$ (Option C)</t>
-  </si>
-  <si>
     <t>$(-1+i)^n$</t>
   </si>
   <si>
@@ -327,9 +294,6 @@
     <t>$(3i)^n$</t>
   </si>
   <si>
-    <t>$(1+i)^n$ (Option C)</t>
-  </si>
-  <si>
     <t>Médiatrice de $[AB]$</t>
   </si>
   <si>
@@ -345,9 +309,6 @@
     <t>$\emptyset$</t>
   </si>
   <si>
-    <t>Médiatrice de $[AB]$ (Option A)</t>
-  </si>
-  <si>
     <t>$z = -3-4i$</t>
   </si>
   <si>
@@ -360,9 +321,6 @@
     <t>Le conjugué de $z$ est $\overline{z}=3+4i$</t>
   </si>
   <si>
-    <t>A et C</t>
-  </si>
-  <si>
     <t>$|z| = \frac{1}{\sqrt[5]{2}}$</t>
   </si>
   <si>
@@ -375,9 +333,6 @@
     <t>$\arg(z) = \frac{\pi}{12} + \frac{2k\pi}{5} [2\pi]$</t>
   </si>
   <si>
-    <t>B et D</t>
-  </si>
-  <si>
     <t>Une droite</t>
   </si>
   <si>
@@ -388,9 +343,6 @@
   </si>
   <si>
     <t>Le cercle de rayon $2$ et centre $-1+2i$</t>
-  </si>
-  <si>
-    <t>Un cercle (Option B)</t>
   </si>
 </sst>
 </file>
@@ -908,7 +860,7 @@
         <v>40</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J2" s="4"/>
     </row>
@@ -926,19 +878,19 @@
         <v>12</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>44</v>
-      </c>
       <c r="I3" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J3" s="5"/>
     </row>
@@ -953,22 +905,22 @@
         <v>3</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="I4" s="10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J4" s="4"/>
     </row>
@@ -983,20 +935,20 @@
         <v>3</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>55</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J5" s="5"/>
     </row>
@@ -1011,22 +963,22 @@
         <v>3</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="I6" s="10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J6" s="4"/>
     </row>
@@ -1041,22 +993,22 @@
         <v>3</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>66</v>
-      </c>
       <c r="I7" s="11" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="J7" s="5"/>
     </row>
@@ -1071,22 +1023,22 @@
         <v>3</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J8" s="4"/>
     </row>
@@ -1101,22 +1053,22 @@
         <v>3</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="J9" s="5"/>
     </row>
@@ -1131,22 +1083,22 @@
         <v>3</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="J10" s="4"/>
     </row>
@@ -1161,22 +1113,22 @@
         <v>3</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J11" s="5"/>
     </row>
@@ -1191,22 +1143,22 @@
         <v>3</v>
       </c>
       <c r="D12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="H12" s="8" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="72" thickBot="1" x14ac:dyDescent="0.3">
@@ -1232,10 +1184,10 @@
         <v>16</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="72" thickBot="1" x14ac:dyDescent="0.3">
@@ -1249,22 +1201,22 @@
         <v>3</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="72" thickBot="1" x14ac:dyDescent="0.3">
@@ -1278,22 +1230,22 @@
         <v>3</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="72" thickBot="1" x14ac:dyDescent="0.3">
@@ -1307,20 +1259,20 @@
         <v>3</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="H16" s="8"/>
-      <c r="I16" s="10" t="s">
-        <v>111</v>
+      <c r="I16" s="8" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="72" thickBot="1" x14ac:dyDescent="0.3">
@@ -1334,20 +1286,20 @@
         <v>3</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="H17" s="9"/>
-      <c r="I17" s="11" t="s">
-        <v>116</v>
+      <c r="I17" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="72" thickBot="1" x14ac:dyDescent="0.3">
@@ -1361,20 +1313,20 @@
         <v>3</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="10" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
